--- a/12625694.xlsx
+++ b/12625694.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahul\Documents\MCA\CAP776(PYTHON)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5675210B-0B1C-4107-A1C0-85EB2E73CB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CEBDAD-AA6B-4F28-A9A7-A7A5039991E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,15 +27,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -219,6 +216,33 @@
   <si>
     <t>SEPTEMBER</t>
   </si>
+  <si>
+    <t>Day went descent</t>
+  </si>
+  <si>
+    <t>Fine</t>
+  </si>
+  <si>
+    <t>Classes felt hectic</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Day went good</t>
+  </si>
+  <si>
+    <t>Had a good rest day</t>
+  </si>
+  <si>
+    <t>Felt low on energy today</t>
+  </si>
+  <si>
+    <t>Day went okay</t>
+  </si>
 </sst>
 </file>
 
@@ -356,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -400,6 +424,96 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1089,136 +1203,268 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+      <c r="A8" s="21">
+        <v>46282</v>
+      </c>
+      <c r="B8" s="22">
+        <v>320</v>
+      </c>
+      <c r="C8" s="22">
+        <v>40</v>
+      </c>
+      <c r="D8" s="22">
+        <v>200</v>
+      </c>
+      <c r="E8" s="22">
+        <v>100</v>
+      </c>
+      <c r="F8" s="22">
+        <v>300</v>
+      </c>
+      <c r="G8" s="22">
+        <v>5</v>
+      </c>
+      <c r="H8" s="22">
+        <v>100</v>
+      </c>
+      <c r="I8" s="23">
+        <v>1080</v>
+      </c>
+      <c r="J8" s="23">
+        <v>360</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="25" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+      <c r="A9" s="26">
+        <v>46283</v>
+      </c>
+      <c r="B9" s="27">
+        <v>340</v>
+      </c>
+      <c r="C9" s="27">
+        <v>30</v>
+      </c>
+      <c r="D9" s="27">
+        <v>120</v>
+      </c>
+      <c r="E9" s="27">
+        <v>110</v>
+      </c>
+      <c r="F9" s="27">
+        <v>350</v>
+      </c>
+      <c r="G9" s="27">
+        <v>6</v>
+      </c>
+      <c r="H9" s="27">
+        <v>120</v>
+      </c>
+      <c r="I9" s="28">
+        <v>1100</v>
+      </c>
+      <c r="J9" s="28">
+        <v>340</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+      <c r="A10" s="31">
+        <v>46284</v>
+      </c>
+      <c r="B10" s="32">
+        <v>400</v>
+      </c>
+      <c r="C10" s="32">
+        <v>90</v>
+      </c>
+      <c r="D10" s="32">
+        <v>180</v>
+      </c>
+      <c r="E10" s="32">
+        <v>90</v>
+      </c>
+      <c r="F10" s="32">
+        <v>50</v>
+      </c>
+      <c r="G10" s="32">
+        <v>1</v>
+      </c>
+      <c r="H10" s="32">
+        <v>150</v>
+      </c>
+      <c r="I10" s="33">
+        <v>995</v>
+      </c>
+      <c r="J10" s="33">
+        <v>445</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" s="35" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+      <c r="A11" s="36">
+        <v>46285</v>
+      </c>
+      <c r="B11" s="37">
+        <v>450</v>
+      </c>
+      <c r="C11" s="37">
+        <v>60</v>
+      </c>
+      <c r="D11" s="37">
+        <v>200</v>
+      </c>
+      <c r="E11" s="37">
+        <v>60</v>
+      </c>
+      <c r="F11" s="37">
+        <v>0</v>
+      </c>
+      <c r="G11" s="37">
+        <v>0</v>
+      </c>
+      <c r="H11" s="37">
+        <v>200</v>
+      </c>
+      <c r="I11" s="38">
+        <v>1020</v>
+      </c>
+      <c r="J11" s="38">
+        <v>420</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="40" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+      <c r="A12" s="41">
+        <v>46286</v>
+      </c>
+      <c r="B12" s="42">
+        <v>350</v>
+      </c>
+      <c r="C12" s="42">
+        <v>100</v>
+      </c>
+      <c r="D12" s="42">
+        <v>180</v>
+      </c>
+      <c r="E12" s="42">
+        <v>110</v>
+      </c>
+      <c r="F12" s="42">
+        <v>200</v>
+      </c>
+      <c r="G12" s="42">
+        <v>6</v>
+      </c>
+      <c r="H12" s="42">
+        <v>200</v>
+      </c>
+      <c r="I12" s="43">
+        <v>1150</v>
+      </c>
+      <c r="J12" s="43">
+        <v>290</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" s="45" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="A13" s="46">
+        <v>46287</v>
+      </c>
+      <c r="B13" s="47">
+        <v>400</v>
+      </c>
+      <c r="C13" s="47">
+        <v>45</v>
+      </c>
+      <c r="D13" s="47">
+        <v>300</v>
+      </c>
+      <c r="E13" s="47">
+        <v>60</v>
+      </c>
+      <c r="F13" s="47">
+        <v>300</v>
+      </c>
+      <c r="G13" s="47">
+        <v>5</v>
+      </c>
+      <c r="H13" s="47">
+        <v>120</v>
+      </c>
+      <c r="I13" s="48">
+        <v>1285</v>
+      </c>
+      <c r="J13" s="48">
+        <v>155</v>
+      </c>
+      <c r="K13" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="50" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
